--- a/光伏配储项目/电价数据/2026/樱花站.xlsx
+++ b/光伏配储项目/电价数据/2026/樱花站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51249</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75528</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.58375</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5843700000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5142599999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42698</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.5412899999999999</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.04022</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.03731</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03365</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.03554</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.04634000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.0235</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02596</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02506</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>-0.04901</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01477</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.02719</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01902</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.04040999999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.04753</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.03789</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.008160000000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19984</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5557000000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39769</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.67924</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.56968</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43353</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43755</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56616</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6039099999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79867</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.62754</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63101</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7388899999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9284</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65967</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58336</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47318</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62391</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60363</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.49992</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44277</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69172</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.00139</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.63728</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.54943</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.66662</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49363</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50492</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48446</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55188</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.49092</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42796</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.24244</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.1893</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.10999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19574</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.23525</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01532</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.15577</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.03992</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.02224</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>-0.00475</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.13153</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.19356</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.01925</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04193</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.03615</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.57945</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.48178</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49301</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.5880599999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5323099999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67148</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.63266</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7192999999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76551</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47093</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.44326</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4357200000000001</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.42704</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42231</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47376</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43949</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.26019</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25925</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25188</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20866</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23254</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43918</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.46881</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.50417</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45701</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46295</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45154</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.5248200000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.60865</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5767599999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5962999999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46362</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48199</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44717</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45848</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44405</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.47652</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12529</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24124</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19757</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.20049</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56036</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21245</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.22495</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.16782</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.11032</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.02548</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.03231000000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.004160000000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.23518</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.02653</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.19433</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19508</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10258</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.10127</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.10168</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16467</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3158</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.21181</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.22089</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.2126</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20687</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.21784</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21385</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.19241</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.0287</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.17862</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09408</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.0362</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03601</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03795</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03878</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04679</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04072</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03825</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04865999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.04042</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05799</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.00851</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03396</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09587999999999999</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35078</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6535599999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44504</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42233</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01044</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20703</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04966</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04040999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.01806</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3353</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31699</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91408</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29601</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88714</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63154</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18673</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8684700000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5360199999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33048</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03266</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53042</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79067</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52964</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77266</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7772899999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87673</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8737</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49286</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39951</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20661</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6214700000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53822</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49758</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5854600000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42706</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5955900000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60121</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69023</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46852</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58021</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85897</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.7827999999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.78811</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.24656</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.5427000000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45166</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3533</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91803</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46368</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4991</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16614</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19891</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19289</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.04525999999999999</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44295</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59515</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45267</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16067</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6998300000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7906599999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6643600000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5790700000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50098</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41521</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5003</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43448</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42774</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4338399999999999</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41314</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49459</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55033</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15521</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01411</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25527</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5698200000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46205</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8472799999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43626</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4568</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32333</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27923</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2254</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14144</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.1451</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15273</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.04186</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.01601</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14129</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13608</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24712</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13659</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.16978</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.03208</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10775</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10734</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12602</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13572</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14059</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44272</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34819</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53706</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42275</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.15993</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.14293</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.00107</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20053</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.16788</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24327</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.00487</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24223</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25972</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35987</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43506</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39104</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.51971</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24951</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27335</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.20853</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.4687</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.23081</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.45486</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6898099999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22197</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31464</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.15237</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.14996</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.19212</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.22286</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.22314</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.22366</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34949</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.03596</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.03443</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.03644</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.00443</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.04672999999999999</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.03491</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.03512</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.03659</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>-0.03197</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.03592</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.03778</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.03578</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.03763</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.19259</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65639</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7699199999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45172</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45744</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34423</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26555</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14848</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.03092</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.02604</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.02651</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19981</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.02155</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21636</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.22834</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43247</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41426</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59784</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60565</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48584</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.81145</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48747</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44317</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48953</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47081</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35983</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48852</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5269400000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4823</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41619</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.10644</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.08395</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.03052</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.04184</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.04668</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.06135</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>-0.00353</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.18567</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.20868</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.04501</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.00704</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.004589999999999999</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>-0.02494</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.04176</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.02938</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>-0.03024</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>-0.03329</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.03365</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>-0.03622</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.03865</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>-0.04491</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>-0.008289999999999999</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>-0.04811</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.22454</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.22416</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.22506</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49193</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43806</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50192</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50515</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54313</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69079</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.71199</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.92289</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.53639</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58233</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52496</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8314199999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7701</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67214</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47167</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4817</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47615</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4689</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55118</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44113</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45503</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45397</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.27824</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.24242</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.27338</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.22513</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.03796</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.03231000000000001</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.05968</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19714</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.05193</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.00941</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04641</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>-0.01217</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.02319</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.03746</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>-0.02295</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.02381</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.01644</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.01556</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.02717</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.03542</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.06618</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.04296</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.2218</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.23482</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.23512</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.24155</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36513</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25484</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.25838</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22982</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22478</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24917</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.22699</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13951</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.25457</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.22449</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.22358</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.01809</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04307</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16929</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18744</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.23474</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23381</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.20479</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.00197</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.19346</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.20213</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.1768</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.21424</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.17521</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.21918</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.22056</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33919</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03867</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03856</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.13718</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.22571</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.53753</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.21923</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.26492</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.2524</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27476</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26657</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.05257</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26974</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6287200000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.76146</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75259</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57809</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.23327</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02726</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22646</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.19985</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.17451</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.01614</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.00835</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.03687</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.02631</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.006860000000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04432</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.04123</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04745000000000001</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.03845000000000001</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.20851</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.20858</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.01546</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.18024</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.1923</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18738</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16043</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.22596</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.26102</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27182</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32153</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.15439</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.52015</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.53124</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.23177</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.17189</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.04976</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.00286</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.06958</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.04083</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.04568</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.23257</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14176</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.23495</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.22616</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.23278</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.22561</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34032</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.83212</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5408200000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.23031</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.23155</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.23044</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.20218</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.03101</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.04915</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.04589</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.23224</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.02916</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.04965</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.19285</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.19173</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.19846</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.04976</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.04226</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.05051</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.04937</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.1832</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.05511</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.23731</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.22082</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.26798</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.46008</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27509</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33039</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.18962</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.23811</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.23823</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.18808</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.22506</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.22216</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.24476</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44732</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.22959</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.23088</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.03835</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.19526</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.04048</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.05618</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.05427000000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.05493</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.23429</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.03304</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.04706</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.05084</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.20254</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.24176</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.23148</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.05884</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.20573</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.25261</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.06692000000000001</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.23525</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.42169</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.44285</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7445499999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.42252</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.33731</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.22508</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.22122</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.26623</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.04068</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.2215</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.23215</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.22967</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.22433</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.03542</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.05003</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.22875</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27259</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.22959</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.20351</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.03749</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.00601</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.21637</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.03526</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.06420000000000001</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.02672</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.00346</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.01283</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01314</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.03285</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08733</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.01067</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.02436</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.01769</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.05414</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.05838</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.05515</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.24044</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.06458</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.06972</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.20852</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.19361</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.23919</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.23087</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.25328</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.22528</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.22489</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.22188</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.17599</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.22438</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.49354</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.22317</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.22269</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.23197</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.23034</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.22432</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.22404</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.04778</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.05342</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.2406</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.20605</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.22017</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.05067</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.04883</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.22815</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.19591</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.01625</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.07240000000000001</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>-0.00223</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.01891</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.008369999999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.03014</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.04803</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.04245</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.03849</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.4978399999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.24207</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.24172</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.49866</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.22618</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.32851</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.03709</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.22365</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.19035</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.22336</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.02796</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.20359</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>-0.00876</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>-0.00433</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.21704</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13135</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>-0.00375</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02078</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.02591</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02296</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08448</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.01328</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.04147</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.02453</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.03668</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.04839</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.04917</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.0471</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.21788</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23102</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.00206</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20012</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.20729</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.22536</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.22567</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2232</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.22554</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.23805</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37711</v>
       </c>
     </row>
   </sheetData>
